--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2016/Aircraft_Cumulative_Statistics_2016.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2016/Aircraft_Cumulative_Statistics_2016.xlsx
@@ -13,72 +13,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="39" uniqueCount="39">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -160,10 +175,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -183,40 +198,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
@@ -224,40 +239,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>31088710289</v>
+        <v>2660824866</v>
       </c>
       <c r="C2" s="0">
-        <v>36367659849</v>
+        <v>3384574193</v>
       </c>
       <c r="D2" s="0">
-        <v>757975</v>
+        <v>143719</v>
       </c>
       <c r="E2" s="0">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>159267</v>
+        <v>169180</v>
       </c>
       <c r="G2" s="0">
-        <v>3.3199999999999998</v>
+        <v>7.1799999999999997</v>
       </c>
       <c r="H2" s="0">
-        <v>11.039999999999999</v>
+        <v>10.82</v>
       </c>
       <c r="I2" s="0">
-        <v>85.480000000000004</v>
+        <v>78.620000000000005</v>
       </c>
       <c r="J2" s="0">
-        <v>1356</v>
+        <v>400</v>
       </c>
       <c r="K2" s="0">
-        <v>2929</v>
+        <v>1260.21</v>
       </c>
       <c r="L2" s="0">
-        <v>17.41</v>
+        <v>25.199999999999999</v>
       </c>
       <c r="M2" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -265,40 +280,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>5655833498</v>
+        <v>6926643940</v>
       </c>
       <c r="C3" s="0">
-        <v>6648761038</v>
+        <v>8661199491</v>
       </c>
       <c r="D3" s="0">
-        <v>528518</v>
+        <v>94928</v>
       </c>
       <c r="E3" s="0">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>40396</v>
+        <v>473188</v>
       </c>
       <c r="G3" s="0">
-        <v>3.21</v>
+        <v>5.1900000000000004</v>
       </c>
       <c r="H3" s="0">
-        <v>7.9000000000000004</v>
+        <v>7.4199999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>85.069999999999993</v>
+        <v>79.969999999999999</v>
       </c>
       <c r="J3" s="0">
-        <v>957</v>
+        <v>366</v>
       </c>
       <c r="K3" s="0">
-        <v>3023</v>
+        <v>1319.7</v>
       </c>
       <c r="L3" s="0">
-        <v>17.629999999999999</v>
+        <v>26.390000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -306,40 +321,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>187081799498</v>
+        <v>1406319209</v>
       </c>
       <c r="C4" s="0">
-        <v>227180769035</v>
+        <v>1741126419</v>
       </c>
       <c r="D4" s="0">
-        <v>724845</v>
+        <v>187419</v>
       </c>
       <c r="E4" s="0">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="F4" s="0">
-        <v>982213</v>
+        <v>40240</v>
       </c>
       <c r="G4" s="0">
-        <v>3.1299999999999999</v>
+        <v>4.3300000000000001</v>
       </c>
       <c r="H4" s="0">
-        <v>10.210000000000001</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I4" s="0">
-        <v>82.349999999999994</v>
+        <v>80.769999999999996</v>
       </c>
       <c r="J4" s="0">
-        <v>1285</v>
+        <v>620</v>
       </c>
       <c r="K4" s="0">
-        <v>4365</v>
+        <v>1101.1900000000001</v>
       </c>
       <c r="L4" s="0">
-        <v>24.870000000000001</v>
+        <v>15.789999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="5">
@@ -347,40 +362,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>160569298355</v>
+        <v>14171235895</v>
       </c>
       <c r="C5" s="0">
-        <v>188635223023</v>
+        <v>17414161064</v>
       </c>
       <c r="D5" s="0">
-        <v>827856</v>
+        <v>251832</v>
       </c>
       <c r="E5" s="0">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="F5" s="0">
-        <v>754470</v>
+        <v>357795</v>
       </c>
       <c r="G5" s="0">
-        <v>3.3100000000000001</v>
+        <v>5.1699999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>10.710000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="I5" s="0">
-        <v>85.120000000000005</v>
+        <v>81.379999999999995</v>
       </c>
       <c r="J5" s="0">
-        <v>1315</v>
+        <v>636</v>
       </c>
       <c r="K5" s="0">
-        <v>4390</v>
+        <v>1268.03</v>
       </c>
       <c r="L5" s="0">
-        <v>23.879999999999999</v>
+        <v>16.550000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.052999999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -388,40 +403,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>16009458178</v>
+        <v>11279145832</v>
       </c>
       <c r="C6" s="0">
-        <v>18358681382</v>
+        <v>13957762636</v>
       </c>
       <c r="D6" s="0">
-        <v>789621</v>
+        <v>179037</v>
       </c>
       <c r="E6" s="0">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c r="F6" s="0">
-        <v>98844</v>
+        <v>384674</v>
       </c>
       <c r="G6" s="0">
-        <v>4.25</v>
+        <v>4.9299999999999997</v>
       </c>
       <c r="H6" s="0">
-        <v>11.949999999999999</v>
+        <v>8.6600000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>87.200000000000003</v>
+        <v>80.810000000000002</v>
       </c>
       <c r="J6" s="0">
-        <v>1066</v>
+        <v>532</v>
       </c>
       <c r="K6" s="0">
-        <v>3251</v>
+        <v>1346.1199999999999</v>
       </c>
       <c r="L6" s="0">
-        <v>18.649999999999999</v>
+        <v>19.75</v>
       </c>
       <c r="M6" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="7">
@@ -429,40 +444,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>15473031571</v>
+        <v>6722341232</v>
       </c>
       <c r="C7" s="0">
-        <v>18349279376</v>
+        <v>8221552967</v>
       </c>
       <c r="D7" s="0">
-        <v>1031438</v>
+        <v>281367</v>
       </c>
       <c r="E7" s="0">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="F7" s="0">
-        <v>81456</v>
+        <v>153100</v>
       </c>
       <c r="G7" s="0">
-        <v>4.5800000000000001</v>
+        <v>5.2400000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>9.8000000000000007</v>
+        <v>9.3300000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>84.329999999999998</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="J7" s="0">
-        <v>844</v>
+        <v>538</v>
       </c>
       <c r="K7" s="0">
-        <v>5729</v>
+        <v>2673.8800000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>23.300000000000001</v>
+        <v>26.800000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="8">
@@ -470,40 +485,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>45672742799</v>
+        <v>14000577378</v>
       </c>
       <c r="C8" s="0">
-        <v>53702185831</v>
+        <v>17627045853</v>
       </c>
       <c r="D8" s="0">
-        <v>670021</v>
+        <v>210196</v>
       </c>
       <c r="E8" s="0">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="F8" s="0">
-        <v>338592</v>
+        <v>425115</v>
       </c>
       <c r="G8" s="0">
-        <v>4.2199999999999998</v>
+        <v>5.0700000000000003</v>
       </c>
       <c r="H8" s="0">
-        <v>12.050000000000001</v>
+        <v>9.1099999999999994</v>
       </c>
       <c r="I8" s="0">
-        <v>85.049999999999997</v>
+        <v>79.430000000000007</v>
       </c>
       <c r="J8" s="0">
-        <v>1095</v>
+        <v>542</v>
       </c>
       <c r="K8" s="0">
-        <v>3051</v>
+        <v>1096.5699999999999</v>
       </c>
       <c r="L8" s="0">
-        <v>21.390000000000001</v>
+        <v>14.35</v>
       </c>
       <c r="M8" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.048000000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -511,40 +526,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>111644441514</v>
+        <v>43152675332</v>
       </c>
       <c r="C9" s="0">
-        <v>132339561463</v>
+        <v>51492402463</v>
       </c>
       <c r="D9" s="0">
-        <v>607983</v>
+        <v>455685</v>
       </c>
       <c r="E9" s="0">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="F9" s="0">
-        <v>1115519</v>
+        <v>445406</v>
       </c>
       <c r="G9" s="0">
-        <v>5.1200000000000001</v>
+        <v>3.9399999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>10.84</v>
+        <v>9.4199999999999999</v>
       </c>
       <c r="I9" s="0">
-        <v>84.359999999999999</v>
+        <v>83.799999999999997</v>
       </c>
       <c r="J9" s="0">
-        <v>790</v>
+        <v>863</v>
       </c>
       <c r="K9" s="0">
-        <v>3319</v>
+        <v>3042.6199999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>22.16</v>
+        <v>22.75</v>
       </c>
       <c r="M9" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="10">
@@ -552,40 +567,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>21582440997</v>
+        <v>88269368992</v>
       </c>
       <c r="C10" s="0">
-        <v>25640537931</v>
+        <v>104005804539</v>
       </c>
       <c r="D10" s="0">
-        <v>812953</v>
+        <v>660187</v>
       </c>
       <c r="E10" s="0">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="F10" s="0">
-        <v>148521</v>
+        <v>618198</v>
       </c>
       <c r="G10" s="0">
-        <v>4.71</v>
+        <v>3.9199999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>12.25</v>
+        <v>10.960000000000001</v>
       </c>
       <c r="I10" s="0">
-        <v>84.170000000000002</v>
+        <v>84.870000000000005</v>
       </c>
       <c r="J10" s="0">
-        <v>986</v>
+        <v>1073</v>
       </c>
       <c r="K10" s="0">
-        <v>2909</v>
+        <v>3345.6799999999998</v>
       </c>
       <c r="L10" s="0">
-        <v>16.609999999999999</v>
+        <v>21.329999999999998</v>
       </c>
       <c r="M10" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -593,40 +608,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>3575164477</v>
+        <v>61747923134</v>
       </c>
       <c r="C11" s="0">
-        <v>4634409672</v>
+        <v>72077858228</v>
       </c>
       <c r="D11" s="0">
-        <v>565172</v>
+        <v>803006</v>
       </c>
       <c r="E11" s="0">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F11" s="0">
-        <v>23300</v>
+        <v>311588</v>
       </c>
       <c r="G11" s="0">
-        <v>2.8399999999999999</v>
+        <v>3.4700000000000002</v>
       </c>
       <c r="H11" s="0">
-        <v>9.0500000000000007</v>
+        <v>11.31</v>
       </c>
       <c r="I11" s="0">
-        <v>77.140000000000001</v>
+        <v>85.670000000000002</v>
       </c>
       <c r="J11" s="0">
-        <v>1286</v>
+        <v>1277</v>
       </c>
       <c r="K11" s="0">
-        <v>3668</v>
+        <v>3672.1900000000001</v>
       </c>
       <c r="L11" s="0">
-        <v>23.73</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="M11" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -634,40 +649,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>173866646288</v>
+        <v>8575303585</v>
       </c>
       <c r="C12" s="0">
-        <v>209258427097</v>
+        <v>10449677932</v>
       </c>
       <c r="D12" s="0">
-        <v>65535</v>
+        <v>265827</v>
       </c>
       <c r="E12" s="0">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="F12" s="0">
-        <v>699145</v>
+        <v>226909</v>
       </c>
       <c r="G12" s="0">
-        <v>65535</v>
+        <v>5.7699999999999996</v>
       </c>
       <c r="H12" s="0">
-        <v>65535</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="I12" s="0">
-        <v>83.090000000000003</v>
+        <v>82.060000000000002</v>
       </c>
       <c r="J12" s="0">
-        <v>1597</v>
+        <v>413</v>
       </c>
       <c r="K12" s="0">
-        <v>4573</v>
+        <v>3449.4200000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>24.989999999999998</v>
+        <v>30.68</v>
       </c>
       <c r="M12" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="13">
@@ -675,40 +690,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>66266136</v>
+        <v>90389697478</v>
       </c>
       <c r="C13" s="0">
-        <v>79181550</v>
+        <v>108101087307</v>
       </c>
       <c r="D13" s="0">
-        <v>65535</v>
+        <v>542731</v>
       </c>
       <c r="E13" s="0">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="F13" s="0">
-        <v>4436</v>
+        <v>1002883</v>
       </c>
       <c r="G13" s="0">
-        <v>65535</v>
+        <v>5.04</v>
       </c>
       <c r="H13" s="0">
-        <v>65535</v>
+        <v>10.460000000000001</v>
       </c>
       <c r="I13" s="0">
-        <v>83.689999999999998</v>
+        <v>83.620000000000005</v>
       </c>
       <c r="J13" s="0">
-        <v>357</v>
+        <v>767</v>
       </c>
       <c r="K13" s="0">
-        <v>0</v>
+        <v>3390.6900000000001</v>
       </c>
       <c r="L13" s="0">
-        <v>0</v>
+        <v>24.120000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -716,40 +731,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>5878711774</v>
+        <v>140790647464</v>
       </c>
       <c r="C14" s="0">
-        <v>7386456017</v>
+        <v>165648490142</v>
       </c>
       <c r="D14" s="0">
-        <v>155832</v>
+        <v>670560</v>
       </c>
       <c r="E14" s="0">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="F14" s="0">
-        <v>209053</v>
+        <v>855257</v>
       </c>
       <c r="G14" s="0">
-        <v>4.4100000000000001</v>
+        <v>3.46</v>
       </c>
       <c r="H14" s="0">
-        <v>7.7699999999999996</v>
+        <v>10.44</v>
       </c>
       <c r="I14" s="0">
-        <v>79.590000000000003</v>
+        <v>84.989999999999995</v>
       </c>
       <c r="J14" s="0">
-        <v>508</v>
+        <v>1184</v>
       </c>
       <c r="K14" s="0">
-        <v>1092</v>
+        <v>3595.27</v>
       </c>
       <c r="L14" s="0">
-        <v>15.960000000000001</v>
+        <v>21.98</v>
       </c>
       <c r="M14" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -757,40 +772,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5047230786</v>
+        <v>37464151182</v>
       </c>
       <c r="C15" s="0">
-        <v>6358070703</v>
+        <v>43860829543</v>
       </c>
       <c r="D15" s="0">
-        <v>184078</v>
+        <v>770976</v>
       </c>
       <c r="E15" s="0">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="F15" s="0">
-        <v>245047</v>
+        <v>192425</v>
       </c>
       <c r="G15" s="0">
-        <v>7.0899999999999999</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>11.4</v>
+        <v>10.890000000000001</v>
       </c>
       <c r="I15" s="0">
-        <v>79.379999999999995</v>
+        <v>85.420000000000002</v>
       </c>
       <c r="J15" s="0">
-        <v>451</v>
+        <v>1293</v>
       </c>
       <c r="K15" s="0">
-        <v>1348</v>
+        <v>3405.48</v>
       </c>
       <c r="L15" s="0">
-        <v>23.640000000000001</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.048000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -798,40 +813,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>2678858895</v>
+        <v>28753046860</v>
       </c>
       <c r="C16" s="0">
-        <v>3380368532</v>
+        <v>32906707555</v>
       </c>
       <c r="D16" s="0">
-        <v>171071</v>
+        <v>856499</v>
       </c>
       <c r="E16" s="0">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="F16" s="0">
-        <v>87364</v>
+        <v>139843</v>
       </c>
       <c r="G16" s="0">
-        <v>4.4199999999999999</v>
+        <v>3.6400000000000001</v>
       </c>
       <c r="H16" s="0">
-        <v>8.1199999999999992</v>
+        <v>11.69</v>
       </c>
       <c r="I16" s="0">
-        <v>79.25</v>
+        <v>87.379999999999995</v>
       </c>
       <c r="J16" s="0">
-        <v>546</v>
+        <v>1304</v>
       </c>
       <c r="K16" s="0">
-        <v>1206</v>
+        <v>3264.3800000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>17.02</v>
+        <v>18.09</v>
       </c>
       <c r="M16" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.044999999999999998</v>
       </c>
     </row>
     <row r="17">
@@ -839,40 +854,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>7538494671</v>
+        <v>53043151453</v>
       </c>
       <c r="C17" s="0">
-        <v>9223368101</v>
+        <v>62042325709</v>
       </c>
       <c r="D17" s="0">
-        <v>231627</v>
+        <v>775045</v>
       </c>
       <c r="E17" s="0">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="F17" s="0">
-        <v>213672</v>
+        <v>208589</v>
       </c>
       <c r="G17" s="0">
-        <v>5.3700000000000001</v>
+        <v>2.6099999999999999</v>
       </c>
       <c r="H17" s="0">
-        <v>9.5800000000000001</v>
+        <v>10.359999999999999</v>
       </c>
       <c r="I17" s="0">
-        <v>81.730000000000004</v>
+        <v>85.5</v>
       </c>
       <c r="J17" s="0">
-        <v>568</v>
+        <v>1677</v>
       </c>
       <c r="K17" s="0">
-        <v>1046</v>
+        <v>4269.3100000000004</v>
       </c>
       <c r="L17" s="0">
-        <v>13.779999999999999</v>
+        <v>24.030000000000001</v>
       </c>
       <c r="M17" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="18">
@@ -880,40 +895,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>81248219</v>
+        <v>10755194299</v>
       </c>
       <c r="C18" s="0">
-        <v>110460143</v>
+        <v>12373005070</v>
       </c>
       <c r="D18" s="0">
-        <v>65535</v>
+        <v>919926</v>
       </c>
       <c r="E18" s="0">
-        <v>50</v>
+        <v>224</v>
       </c>
       <c r="F18" s="0">
-        <v>7118</v>
+        <v>36434</v>
       </c>
       <c r="G18" s="0">
-        <v>65535</v>
+        <v>2.71</v>
       </c>
       <c r="H18" s="0">
-        <v>65535</v>
+        <v>9.9000000000000004</v>
       </c>
       <c r="I18" s="0">
-        <v>73.549999999999997</v>
+        <v>86.920000000000002</v>
       </c>
       <c r="J18" s="0">
-        <v>310</v>
+        <v>1525</v>
       </c>
       <c r="K18" s="0">
-        <v>0</v>
+        <v>4561.8199999999997</v>
       </c>
       <c r="L18" s="0">
-        <v>0</v>
+        <v>20.469999999999999</v>
       </c>
       <c r="M18" s="0">
-        <v>0</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="19">
@@ -921,40 +936,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>4574354058</v>
+        <v>46701276480</v>
       </c>
       <c r="C19" s="0">
-        <v>5860271779</v>
+        <v>58279479500</v>
       </c>
       <c r="D19" s="0">
-        <v>144164</v>
+        <v>1061750</v>
       </c>
       <c r="E19" s="0">
-        <v>66</v>
+        <v>219</v>
       </c>
       <c r="F19" s="0">
-        <v>227799</v>
+        <v>85247</v>
       </c>
       <c r="G19" s="0">
-        <v>5.5999999999999996</v>
+        <v>1.55</v>
       </c>
       <c r="H19" s="0">
-        <v>8.3000000000000007</v>
+        <v>10.640000000000001</v>
       </c>
       <c r="I19" s="0">
-        <v>78.060000000000002</v>
+        <v>80.129999999999995</v>
       </c>
       <c r="J19" s="0">
-        <v>387</v>
+        <v>3179</v>
       </c>
       <c r="K19" s="0">
-        <v>1352</v>
+        <v>5760.71</v>
       </c>
       <c r="L19" s="0">
-        <v>20.399999999999999</v>
+        <v>26.739999999999998</v>
       </c>
       <c r="M19" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="20">
@@ -962,40 +977,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>7032000096</v>
+        <v>15240285240</v>
       </c>
       <c r="C20" s="0">
-        <v>9055693007</v>
+        <v>19478562981</v>
       </c>
       <c r="D20" s="0">
-        <v>208994</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>76</v>
+        <v>244</v>
       </c>
       <c r="F20" s="0">
-        <v>214435</v>
+        <v>20232</v>
       </c>
       <c r="G20" s="0">
-        <v>4.9500000000000002</v>
+        <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>9.4299999999999997</v>
+        <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>77.650000000000006</v>
+        <v>78.239999999999995</v>
       </c>
       <c r="J20" s="0">
-        <v>557</v>
+        <v>3948</v>
       </c>
       <c r="K20" s="0">
-        <v>1346</v>
+        <v>5665.25</v>
       </c>
       <c r="L20" s="0">
-        <v>17.739999999999998</v>
+        <v>23.23</v>
       </c>
       <c r="M20" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.048000000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1003,40 +1018,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>17547582485</v>
+        <v>22134062791</v>
       </c>
       <c r="C21" s="0">
-        <v>21331999824</v>
+        <v>27108775822</v>
       </c>
       <c r="D21" s="0">
-        <v>164662</v>
+        <v>1544660</v>
       </c>
       <c r="E21" s="0">
-        <v>61</v>
+        <v>271</v>
       </c>
       <c r="F21" s="0">
-        <v>641268</v>
+        <v>29732</v>
       </c>
       <c r="G21" s="0">
-        <v>4.9500000000000002</v>
+        <v>1.6899999999999999</v>
       </c>
       <c r="H21" s="0">
-        <v>8.5800000000000001</v>
+        <v>12.25</v>
       </c>
       <c r="I21" s="0">
-        <v>82.260000000000005</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="J21" s="0">
-        <v>516</v>
+        <v>3402</v>
       </c>
       <c r="K21" s="0">
-        <v>1294</v>
+        <v>6329.8999999999996</v>
       </c>
       <c r="L21" s="0">
-        <v>20.52</v>
+        <v>23.579999999999998</v>
       </c>
       <c r="M21" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="22">
@@ -1044,40 +1059,245 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
+        <v>20726284331</v>
+      </c>
+      <c r="C22" s="0">
+        <v>24947877361</v>
+      </c>
+      <c r="D22" s="0">
+        <v>1872964</v>
+      </c>
+      <c r="E22" s="0">
+        <v>291</v>
+      </c>
+      <c r="F22" s="0">
+        <v>21923</v>
+      </c>
+      <c r="G22" s="0">
+        <v>1.6499999999999999</v>
+      </c>
+      <c r="H22" s="0">
+        <v>13.470000000000001</v>
+      </c>
+      <c r="I22" s="0">
+        <v>83.079999999999998</v>
+      </c>
+      <c r="J22" s="0">
+        <v>3907</v>
+      </c>
+      <c r="K22" s="0">
+        <v>6203.6300000000001</v>
+      </c>
+      <c r="L22" s="0">
+        <v>21.300000000000001</v>
+      </c>
+      <c r="M22" s="0">
+        <v>0.044999999999999998</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="0">
+        <v>11677501261</v>
+      </c>
+      <c r="C23" s="0">
+        <v>14262624251</v>
+      </c>
+      <c r="D23" s="0">
+        <v>1379364</v>
+      </c>
+      <c r="E23" s="0">
+        <v>222</v>
+      </c>
+      <c r="F23" s="0">
+        <v>12956</v>
+      </c>
+      <c r="G23" s="0">
+        <v>1.25</v>
+      </c>
+      <c r="H23" s="0">
+        <v>12.289999999999999</v>
+      </c>
+      <c r="I23" s="0">
+        <v>81.870000000000005</v>
+      </c>
+      <c r="J23" s="0">
+        <v>4945</v>
+      </c>
+      <c r="K23" s="0">
+        <v>6566.8400000000001</v>
+      </c>
+      <c r="L23" s="0">
+        <v>29.5</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0.058000000000000003</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>8870604925</v>
+      </c>
+      <c r="C24" s="0">
+        <v>10731443053</v>
+      </c>
+      <c r="D24" s="0">
+        <v>1661214</v>
+      </c>
+      <c r="E24" s="0">
+        <v>253</v>
+      </c>
+      <c r="F24" s="0">
+        <v>7415</v>
+      </c>
+      <c r="G24" s="0">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H24" s="0">
+        <v>12.710000000000001</v>
+      </c>
+      <c r="I24" s="0">
+        <v>82.659999999999997</v>
+      </c>
+      <c r="J24" s="0">
+        <v>5724</v>
+      </c>
+      <c r="K24" s="0">
+        <v>6276.3599999999997</v>
+      </c>
+      <c r="L24" s="0">
+        <v>24.82</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.048000000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>65346030208</v>
+      </c>
+      <c r="C25" s="0">
+        <v>80073867608</v>
+      </c>
+      <c r="D25" s="0">
+        <v>1579678</v>
+      </c>
+      <c r="E25" s="0">
+        <v>274</v>
+      </c>
+      <c r="F25" s="0">
+        <v>63590</v>
+      </c>
+      <c r="G25" s="0">
+        <v>1.25</v>
+      </c>
+      <c r="H25" s="0">
+        <v>11.67</v>
+      </c>
+      <c r="I25" s="0">
+        <v>81.609999999999999</v>
+      </c>
+      <c r="J25" s="0">
+        <v>4639</v>
+      </c>
+      <c r="K25" s="0">
+        <v>8206.9500000000007</v>
+      </c>
+      <c r="L25" s="0">
+        <v>30.23</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.060999999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>11860021217</v>
+      </c>
+      <c r="C26" s="0">
+        <v>15053123666</v>
+      </c>
+      <c r="D26" s="0">
+        <v>2105332</v>
+      </c>
+      <c r="E26" s="0">
+        <v>310</v>
+      </c>
+      <c r="F26" s="0">
+        <v>9996</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H26" s="0">
+        <v>13.619999999999999</v>
+      </c>
+      <c r="I26" s="0">
+        <v>78.790000000000006</v>
+      </c>
+      <c r="J26" s="0">
+        <v>4859</v>
+      </c>
+      <c r="K26" s="0">
+        <v>10408.68</v>
+      </c>
+      <c r="L26" s="0">
+        <v>33.579999999999998</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
         <v>822664314584</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C27" s="0">
         <v>983901365353</v>
       </c>
-      <c r="D22" s="0">
-        <v>65535</v>
-      </c>
-      <c r="E22" s="0">
+      <c r="D27" s="0">
+        <v>0</v>
+      </c>
+      <c r="E27" s="0">
         <v>131</v>
       </c>
-      <c r="F22" s="0">
+      <c r="F27" s="0">
         <v>6291915</v>
       </c>
-      <c r="G22" s="0">
-        <v>65535</v>
-      </c>
-      <c r="H22" s="0">
-        <v>65535</v>
-      </c>
-      <c r="I22" s="0">
+      <c r="G27" s="0">
+        <v>0</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0</v>
+      </c>
+      <c r="I27" s="0">
         <v>83.609999999999999</v>
       </c>
-      <c r="J22" s="0">
+      <c r="J27" s="0">
         <v>978</v>
       </c>
-      <c r="K22" s="0">
-        <v>3470</v>
-      </c>
-      <c r="L22" s="0">
+      <c r="K27" s="0">
+        <v>3469.8299999999999</v>
+      </c>
+      <c r="L27" s="0">
         <v>22.91</v>
       </c>
-      <c r="M22" s="0">
-        <v>0.059999999999999998</v>
+      <c r="M27" s="0">
+        <v>0.058000000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2016/Aircraft_Cumulative_Statistics_2016.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2016/Aircraft_Cumulative_Statistics_2016.xlsx
@@ -13,11 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
   <si>
     <t>Row</t>
   </si>
   <si>
+    <t>E140</t>
+  </si>
+  <si>
     <t>E145</t>
   </si>
   <si>
@@ -30,6 +33,18 @@
     <t>E175</t>
   </si>
   <si>
+    <t>Q100</t>
+  </si>
+  <si>
+    <t>Q200</t>
+  </si>
+  <si>
+    <t>Q300</t>
+  </si>
+  <si>
+    <t>Q400</t>
+  </si>
+  <si>
     <t>CRJ-700</t>
   </si>
   <si>
@@ -48,7 +63,22 @@
     <t>A321</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
+    <t>MD-90</t>
+  </si>
+  <si>
     <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-300</t>
+  </si>
+  <si>
+    <t>B737-400</t>
+  </si>
+  <si>
+    <t>B737-500</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -175,7 +205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -198,40 +228,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -239,40 +269,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2660824866</v>
+        <v>372393886</v>
       </c>
       <c r="C2" s="0">
-        <v>3384574193</v>
+        <v>474091068</v>
       </c>
       <c r="D2" s="0">
-        <v>143719</v>
+        <v>130604</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F2" s="0">
-        <v>169180</v>
+        <v>30917</v>
       </c>
       <c r="G2" s="0">
-        <v>7.1799999999999997</v>
+        <v>8.5199999999999996</v>
       </c>
       <c r="H2" s="0">
-        <v>10.82</v>
+        <v>11.699999999999999</v>
       </c>
       <c r="I2" s="0">
-        <v>78.620000000000005</v>
+        <v>78.549999999999997</v>
       </c>
       <c r="J2" s="0">
-        <v>400</v>
+        <v>349</v>
       </c>
       <c r="K2" s="0">
-        <v>1260.21</v>
+        <v>1345.26</v>
       </c>
       <c r="L2" s="0">
-        <v>25.199999999999999</v>
+        <v>30.57</v>
       </c>
       <c r="M2" s="0">
-        <v>0.095000000000000001</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="3">
@@ -280,40 +310,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>6926643940</v>
+        <v>2660824866</v>
       </c>
       <c r="C3" s="0">
-        <v>8661199491</v>
+        <v>3384574193</v>
       </c>
       <c r="D3" s="0">
-        <v>94928</v>
+        <v>143719</v>
       </c>
       <c r="E3" s="0">
         <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>473188</v>
+        <v>169180</v>
       </c>
       <c r="G3" s="0">
-        <v>5.1900000000000004</v>
+        <v>7.1799999999999997</v>
       </c>
       <c r="H3" s="0">
-        <v>7.4199999999999999</v>
+        <v>10.82</v>
       </c>
       <c r="I3" s="0">
-        <v>79.969999999999999</v>
+        <v>78.620000000000005</v>
       </c>
       <c r="J3" s="0">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="K3" s="0">
-        <v>1319.7</v>
+        <v>1260.21</v>
       </c>
       <c r="L3" s="0">
-        <v>26.390000000000001</v>
+        <v>25.199999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>0.10299999999999999</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -321,40 +351,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>1406319209</v>
+        <v>6926643940</v>
       </c>
       <c r="C4" s="0">
-        <v>1741126419</v>
+        <v>8661199491</v>
       </c>
       <c r="D4" s="0">
-        <v>187419</v>
+        <v>94928</v>
       </c>
       <c r="E4" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F4" s="0">
-        <v>40240</v>
+        <v>473188</v>
       </c>
       <c r="G4" s="0">
-        <v>4.3300000000000001</v>
+        <v>5.1900000000000004</v>
       </c>
       <c r="H4" s="0">
-        <v>8.8000000000000007</v>
+        <v>7.4199999999999999</v>
       </c>
       <c r="I4" s="0">
-        <v>80.769999999999996</v>
+        <v>79.969999999999999</v>
       </c>
       <c r="J4" s="0">
-        <v>620</v>
+        <v>366</v>
       </c>
       <c r="K4" s="0">
-        <v>1101.1900000000001</v>
+        <v>1319.7</v>
       </c>
       <c r="L4" s="0">
-        <v>15.789999999999999</v>
+        <v>26.390000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.051999999999999998</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -362,40 +392,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>14171235895</v>
+        <v>1406319209</v>
       </c>
       <c r="C5" s="0">
-        <v>17414161064</v>
+        <v>1741126419</v>
       </c>
       <c r="D5" s="0">
-        <v>251832</v>
+        <v>187419</v>
       </c>
       <c r="E5" s="0">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F5" s="0">
-        <v>357795</v>
+        <v>40240</v>
       </c>
       <c r="G5" s="0">
-        <v>5.1699999999999999</v>
+        <v>4.3300000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>10.49</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I5" s="0">
-        <v>81.379999999999995</v>
+        <v>80.769999999999996</v>
       </c>
       <c r="J5" s="0">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="K5" s="0">
-        <v>1268.03</v>
+        <v>1101.1900000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>16.550000000000001</v>
+        <v>15.789999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.052999999999999999</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="6">
@@ -403,40 +433,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>11279145832</v>
+        <v>14171235895</v>
       </c>
       <c r="C6" s="0">
-        <v>13957762636</v>
+        <v>17414161064</v>
       </c>
       <c r="D6" s="0">
-        <v>179037</v>
+        <v>251832</v>
       </c>
       <c r="E6" s="0">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F6" s="0">
-        <v>384674</v>
+        <v>357795</v>
       </c>
       <c r="G6" s="0">
-        <v>4.9299999999999997</v>
+        <v>5.1699999999999999</v>
       </c>
       <c r="H6" s="0">
-        <v>8.6600000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="I6" s="0">
-        <v>80.810000000000002</v>
+        <v>81.379999999999995</v>
       </c>
       <c r="J6" s="0">
-        <v>532</v>
+        <v>636</v>
       </c>
       <c r="K6" s="0">
-        <v>1346.1199999999999</v>
+        <v>1268.03</v>
       </c>
       <c r="L6" s="0">
-        <v>19.75</v>
+        <v>16.550000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.052999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -444,40 +474,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>6722341232</v>
+        <v>223459031</v>
       </c>
       <c r="C7" s="0">
-        <v>8221552967</v>
+        <v>321286234</v>
       </c>
       <c r="D7" s="0">
-        <v>281367</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="F7" s="0">
-        <v>153100</v>
+        <v>50285</v>
       </c>
       <c r="G7" s="0">
-        <v>5.2400000000000002</v>
+        <v>0</v>
       </c>
       <c r="H7" s="0">
-        <v>9.3300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0">
-        <v>81.760000000000005</v>
+        <v>69.549999999999997</v>
       </c>
       <c r="J7" s="0">
-        <v>538</v>
+        <v>173</v>
       </c>
       <c r="K7" s="0">
-        <v>2673.8800000000001</v>
+        <v>0</v>
       </c>
       <c r="L7" s="0">
-        <v>26.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="M7" s="0">
-        <v>0.088999999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -485,40 +515,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>14000577378</v>
+        <v>156280534</v>
       </c>
       <c r="C8" s="0">
-        <v>17627045853</v>
+        <v>195512514</v>
       </c>
       <c r="D8" s="0">
-        <v>210196</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F8" s="0">
-        <v>425115</v>
+        <v>27249</v>
       </c>
       <c r="G8" s="0">
-        <v>5.0700000000000003</v>
+        <v>0</v>
       </c>
       <c r="H8" s="0">
-        <v>9.1099999999999994</v>
+        <v>0</v>
       </c>
       <c r="I8" s="0">
-        <v>79.430000000000007</v>
+        <v>79.930000000000007</v>
       </c>
       <c r="J8" s="0">
-        <v>542</v>
+        <v>194</v>
       </c>
       <c r="K8" s="0">
-        <v>1096.5699999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" s="0">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="M8" s="0">
-        <v>0.048000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -526,40 +556,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>43152675332</v>
+        <v>236279013</v>
       </c>
       <c r="C9" s="0">
-        <v>51492402463</v>
+        <v>304261346</v>
       </c>
       <c r="D9" s="0">
-        <v>455685</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="F9" s="0">
-        <v>445406</v>
+        <v>35172</v>
       </c>
       <c r="G9" s="0">
-        <v>3.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="H9" s="0">
-        <v>9.4199999999999999</v>
+        <v>0</v>
       </c>
       <c r="I9" s="0">
-        <v>83.799999999999997</v>
+        <v>77.659999999999997</v>
       </c>
       <c r="J9" s="0">
-        <v>863</v>
+        <v>176</v>
       </c>
       <c r="K9" s="0">
-        <v>3042.6199999999999</v>
+        <v>0</v>
       </c>
       <c r="L9" s="0">
-        <v>22.75</v>
+        <v>0</v>
       </c>
       <c r="M9" s="0">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -567,40 +597,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>88269368992</v>
+        <v>2295911588</v>
       </c>
       <c r="C10" s="0">
-        <v>104005804539</v>
+        <v>2925328721</v>
       </c>
       <c r="D10" s="0">
-        <v>660187</v>
+        <v>149863</v>
       </c>
       <c r="E10" s="0">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="F10" s="0">
-        <v>618198</v>
+        <v>134523</v>
       </c>
       <c r="G10" s="0">
-        <v>3.9199999999999999</v>
+        <v>6.8899999999999997</v>
       </c>
       <c r="H10" s="0">
-        <v>10.960000000000001</v>
+        <v>8.0800000000000001</v>
       </c>
       <c r="I10" s="0">
-        <v>84.870000000000005</v>
+        <v>78.480000000000004</v>
       </c>
       <c r="J10" s="0">
-        <v>1073</v>
+        <v>286</v>
       </c>
       <c r="K10" s="0">
-        <v>3345.6799999999998</v>
+        <v>1520.8699999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>21.329999999999998</v>
+        <v>20.030000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="11">
@@ -608,40 +638,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>61747923134</v>
+        <v>11279145832</v>
       </c>
       <c r="C11" s="0">
-        <v>72077858228</v>
+        <v>13957762636</v>
       </c>
       <c r="D11" s="0">
-        <v>803006</v>
+        <v>179037</v>
       </c>
       <c r="E11" s="0">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="F11" s="0">
-        <v>311588</v>
+        <v>384674</v>
       </c>
       <c r="G11" s="0">
-        <v>3.4700000000000002</v>
+        <v>4.9299999999999997</v>
       </c>
       <c r="H11" s="0">
-        <v>11.31</v>
+        <v>8.6600000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>85.670000000000002</v>
+        <v>80.810000000000002</v>
       </c>
       <c r="J11" s="0">
-        <v>1277</v>
+        <v>532</v>
       </c>
       <c r="K11" s="0">
-        <v>3672.1900000000001</v>
+        <v>1346.1199999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>20.190000000000001</v>
+        <v>19.75</v>
       </c>
       <c r="M11" s="0">
-        <v>0.051999999999999998</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="12">
@@ -649,40 +679,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>8575303585</v>
+        <v>6722341232</v>
       </c>
       <c r="C12" s="0">
-        <v>10449677932</v>
+        <v>8221552967</v>
       </c>
       <c r="D12" s="0">
-        <v>265827</v>
+        <v>281367</v>
       </c>
       <c r="E12" s="0">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F12" s="0">
-        <v>226909</v>
+        <v>153100</v>
       </c>
       <c r="G12" s="0">
-        <v>5.7699999999999996</v>
+        <v>5.2400000000000002</v>
       </c>
       <c r="H12" s="0">
-        <v>8.2899999999999991</v>
+        <v>9.3300000000000001</v>
       </c>
       <c r="I12" s="0">
-        <v>82.060000000000002</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="J12" s="0">
-        <v>413</v>
+        <v>538</v>
       </c>
       <c r="K12" s="0">
-        <v>3449.4200000000001</v>
+        <v>2673.8800000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>30.68</v>
+        <v>26.800000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.108</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="13">
@@ -690,40 +720,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>90389697478</v>
+        <v>14000577378</v>
       </c>
       <c r="C13" s="0">
-        <v>108101087307</v>
+        <v>17627045853</v>
       </c>
       <c r="D13" s="0">
-        <v>542731</v>
+        <v>210196</v>
       </c>
       <c r="E13" s="0">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="F13" s="0">
-        <v>1002883</v>
+        <v>425115</v>
       </c>
       <c r="G13" s="0">
-        <v>5.04</v>
+        <v>5.0700000000000003</v>
       </c>
       <c r="H13" s="0">
-        <v>10.460000000000001</v>
+        <v>9.1099999999999994</v>
       </c>
       <c r="I13" s="0">
-        <v>83.620000000000005</v>
+        <v>79.430000000000007</v>
       </c>
       <c r="J13" s="0">
-        <v>767</v>
+        <v>542</v>
       </c>
       <c r="K13" s="0">
-        <v>3390.6900000000001</v>
+        <v>1096.5699999999999</v>
       </c>
       <c r="L13" s="0">
-        <v>24.120000000000001</v>
+        <v>14.35</v>
       </c>
       <c r="M13" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.048000000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -731,40 +761,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>140790647464</v>
+        <v>43152675332</v>
       </c>
       <c r="C14" s="0">
-        <v>165648490142</v>
+        <v>51492402463</v>
       </c>
       <c r="D14" s="0">
-        <v>670560</v>
+        <v>455685</v>
       </c>
       <c r="E14" s="0">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="F14" s="0">
-        <v>855257</v>
+        <v>445406</v>
       </c>
       <c r="G14" s="0">
-        <v>3.46</v>
+        <v>3.9399999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>10.44</v>
+        <v>9.4199999999999999</v>
       </c>
       <c r="I14" s="0">
-        <v>84.989999999999995</v>
+        <v>83.799999999999997</v>
       </c>
       <c r="J14" s="0">
-        <v>1184</v>
+        <v>863</v>
       </c>
       <c r="K14" s="0">
-        <v>3595.27</v>
+        <v>3042.6199999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>21.98</v>
+        <v>22.75</v>
       </c>
       <c r="M14" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="15">
@@ -772,40 +802,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>37464151182</v>
+        <v>88269368992</v>
       </c>
       <c r="C15" s="0">
-        <v>43860829543</v>
+        <v>104005804539</v>
       </c>
       <c r="D15" s="0">
-        <v>770976</v>
+        <v>660187</v>
       </c>
       <c r="E15" s="0">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="F15" s="0">
-        <v>192425</v>
+        <v>618198</v>
       </c>
       <c r="G15" s="0">
-        <v>3.3799999999999999</v>
+        <v>3.9199999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>10.890000000000001</v>
+        <v>10.960000000000001</v>
       </c>
       <c r="I15" s="0">
-        <v>85.420000000000002</v>
+        <v>84.870000000000005</v>
       </c>
       <c r="J15" s="0">
-        <v>1293</v>
+        <v>1073</v>
       </c>
       <c r="K15" s="0">
-        <v>3405.48</v>
+        <v>3345.6799999999998</v>
       </c>
       <c r="L15" s="0">
-        <v>19.309999999999999</v>
+        <v>21.329999999999998</v>
       </c>
       <c r="M15" s="0">
-        <v>0.048000000000000001</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -813,40 +843,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>28753046860</v>
+        <v>61747923134</v>
       </c>
       <c r="C16" s="0">
-        <v>32906707555</v>
+        <v>72077858228</v>
       </c>
       <c r="D16" s="0">
-        <v>856499</v>
+        <v>803006</v>
       </c>
       <c r="E16" s="0">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F16" s="0">
-        <v>139843</v>
+        <v>311588</v>
       </c>
       <c r="G16" s="0">
-        <v>3.6400000000000001</v>
+        <v>3.4700000000000002</v>
       </c>
       <c r="H16" s="0">
-        <v>11.69</v>
+        <v>11.31</v>
       </c>
       <c r="I16" s="0">
-        <v>87.379999999999995</v>
+        <v>85.670000000000002</v>
       </c>
       <c r="J16" s="0">
-        <v>1304</v>
+        <v>1277</v>
       </c>
       <c r="K16" s="0">
-        <v>3264.3800000000001</v>
+        <v>3672.1900000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>18.09</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="M16" s="0">
-        <v>0.044999999999999998</v>
+        <v>0.051999999999999998</v>
       </c>
     </row>
     <row r="17">
@@ -854,40 +884,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>53043151453</v>
+        <v>28469989333</v>
       </c>
       <c r="C17" s="0">
-        <v>62042325709</v>
+        <v>34203246478</v>
       </c>
       <c r="D17" s="0">
-        <v>775045</v>
+        <v>385128</v>
       </c>
       <c r="E17" s="0">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="F17" s="0">
-        <v>208589</v>
+        <v>361549</v>
       </c>
       <c r="G17" s="0">
-        <v>2.6099999999999999</v>
+        <v>4.0700000000000003</v>
       </c>
       <c r="H17" s="0">
-        <v>10.359999999999999</v>
+        <v>7.8099999999999996</v>
       </c>
       <c r="I17" s="0">
-        <v>85.5</v>
+        <v>83.239999999999995</v>
       </c>
       <c r="J17" s="0">
-        <v>1677</v>
+        <v>638</v>
       </c>
       <c r="K17" s="0">
-        <v>4269.3100000000004</v>
+        <v>3667.0100000000002</v>
       </c>
       <c r="L17" s="0">
-        <v>24.030000000000001</v>
+        <v>24.789999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.073999999999999996</v>
       </c>
     </row>
     <row r="18">
@@ -895,40 +925,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>10755194299</v>
+        <v>10080294907</v>
       </c>
       <c r="C18" s="0">
-        <v>12373005070</v>
+        <v>11673992251</v>
       </c>
       <c r="D18" s="0">
-        <v>919926</v>
+        <v>498889</v>
       </c>
       <c r="E18" s="0">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="F18" s="0">
-        <v>36434</v>
+        <v>101778</v>
       </c>
       <c r="G18" s="0">
-        <v>2.71</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="H18" s="0">
-        <v>9.9000000000000004</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="I18" s="0">
-        <v>86.920000000000002</v>
+        <v>86.349999999999994</v>
       </c>
       <c r="J18" s="0">
-        <v>1525</v>
+        <v>717</v>
       </c>
       <c r="K18" s="0">
-        <v>4561.8199999999997</v>
+        <v>3787.8899999999999</v>
       </c>
       <c r="L18" s="0">
-        <v>20.469999999999999</v>
+        <v>23.68</v>
       </c>
       <c r="M18" s="0">
-        <v>0.049000000000000002</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="19">
@@ -936,40 +966,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>46701276480</v>
+        <v>8575303585</v>
       </c>
       <c r="C19" s="0">
-        <v>58279479500</v>
+        <v>10449677932</v>
       </c>
       <c r="D19" s="0">
-        <v>1061750</v>
+        <v>265827</v>
       </c>
       <c r="E19" s="0">
-        <v>219</v>
+        <v>115</v>
       </c>
       <c r="F19" s="0">
-        <v>85247</v>
+        <v>226909</v>
       </c>
       <c r="G19" s="0">
-        <v>1.55</v>
+        <v>5.7699999999999996</v>
       </c>
       <c r="H19" s="0">
-        <v>10.640000000000001</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="I19" s="0">
-        <v>80.129999999999995</v>
+        <v>82.060000000000002</v>
       </c>
       <c r="J19" s="0">
-        <v>3179</v>
+        <v>413</v>
       </c>
       <c r="K19" s="0">
-        <v>5760.71</v>
+        <v>3449.4200000000001</v>
       </c>
       <c r="L19" s="0">
-        <v>26.739999999999998</v>
+        <v>30.68</v>
       </c>
       <c r="M19" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="20">
@@ -977,40 +1007,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>15240285240</v>
+        <v>12802094130</v>
       </c>
       <c r="C20" s="0">
-        <v>19478562981</v>
+        <v>15714941080</v>
       </c>
       <c r="D20" s="0">
-        <v>0</v>
+        <v>410956</v>
       </c>
       <c r="E20" s="0">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="F20" s="0">
-        <v>20232</v>
+        <v>181702</v>
       </c>
       <c r="G20" s="0">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="H20" s="0">
-        <v>0</v>
+        <v>8.4900000000000002</v>
       </c>
       <c r="I20" s="0">
-        <v>78.239999999999995</v>
+        <v>81.459999999999994</v>
       </c>
       <c r="J20" s="0">
-        <v>3948</v>
+        <v>611</v>
       </c>
       <c r="K20" s="0">
-        <v>5665.25</v>
+        <v>3940.4499999999998</v>
       </c>
       <c r="L20" s="0">
-        <v>23.23</v>
+        <v>27.829999999999998</v>
       </c>
       <c r="M20" s="0">
-        <v>0.048000000000000001</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="21">
@@ -1018,40 +1048,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>22134062791</v>
+        <v>2073383432</v>
       </c>
       <c r="C21" s="0">
-        <v>27108775822</v>
+        <v>2766049451</v>
       </c>
       <c r="D21" s="0">
-        <v>1544660</v>
+        <v>375312</v>
       </c>
       <c r="E21" s="0">
-        <v>271</v>
+        <v>127</v>
       </c>
       <c r="F21" s="0">
-        <v>29732</v>
+        <v>34525</v>
       </c>
       <c r="G21" s="0">
-        <v>1.6899999999999999</v>
+        <v>4.6799999999999997</v>
       </c>
       <c r="H21" s="0">
-        <v>12.25</v>
+        <v>8.1899999999999995</v>
       </c>
       <c r="I21" s="0">
-        <v>81.650000000000006</v>
+        <v>74.959999999999994</v>
       </c>
       <c r="J21" s="0">
-        <v>3402</v>
+        <v>609</v>
       </c>
       <c r="K21" s="0">
-        <v>6329.8999999999996</v>
+        <v>3605.71</v>
       </c>
       <c r="L21" s="0">
-        <v>23.579999999999998</v>
+        <v>27.440000000000001</v>
       </c>
       <c r="M21" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1059,40 +1089,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>20726284331</v>
+        <v>411845711</v>
       </c>
       <c r="C22" s="0">
-        <v>24947877361</v>
+        <v>534220066</v>
       </c>
       <c r="D22" s="0">
-        <v>1872964</v>
+        <v>237431</v>
       </c>
       <c r="E22" s="0">
-        <v>291</v>
+        <v>122</v>
       </c>
       <c r="F22" s="0">
-        <v>21923</v>
+        <v>14376</v>
       </c>
       <c r="G22" s="0">
-        <v>1.6499999999999999</v>
+        <v>6.3899999999999997</v>
       </c>
       <c r="H22" s="0">
-        <v>13.470000000000001</v>
+        <v>7.0199999999999996</v>
       </c>
       <c r="I22" s="0">
-        <v>83.079999999999998</v>
+        <v>77.090000000000003</v>
       </c>
       <c r="J22" s="0">
-        <v>3907</v>
+        <v>305</v>
       </c>
       <c r="K22" s="0">
-        <v>6203.6300000000001</v>
+        <v>3153.3400000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>21.300000000000001</v>
+        <v>25.850000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.044999999999999998</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1100,40 +1130,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>11677501261</v>
+        <v>90389697478</v>
       </c>
       <c r="C23" s="0">
-        <v>14262624251</v>
+        <v>108101087307</v>
       </c>
       <c r="D23" s="0">
-        <v>1379364</v>
+        <v>542731</v>
       </c>
       <c r="E23" s="0">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="F23" s="0">
-        <v>12956</v>
+        <v>1002883</v>
       </c>
       <c r="G23" s="0">
-        <v>1.25</v>
+        <v>5.04</v>
       </c>
       <c r="H23" s="0">
-        <v>12.289999999999999</v>
+        <v>10.460000000000001</v>
       </c>
       <c r="I23" s="0">
-        <v>81.870000000000005</v>
+        <v>83.620000000000005</v>
       </c>
       <c r="J23" s="0">
-        <v>4945</v>
+        <v>767</v>
       </c>
       <c r="K23" s="0">
-        <v>6566.8400000000001</v>
+        <v>3390.6900000000001</v>
       </c>
       <c r="L23" s="0">
-        <v>29.5</v>
+        <v>24.120000000000001</v>
       </c>
       <c r="M23" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="24">
@@ -1141,40 +1171,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>8870604925</v>
+        <v>140790647464</v>
       </c>
       <c r="C24" s="0">
-        <v>10731443053</v>
+        <v>165648490142</v>
       </c>
       <c r="D24" s="0">
-        <v>1661214</v>
+        <v>670560</v>
       </c>
       <c r="E24" s="0">
-        <v>253</v>
+        <v>164</v>
       </c>
       <c r="F24" s="0">
-        <v>7415</v>
+        <v>855257</v>
       </c>
       <c r="G24" s="0">
-        <v>1.1499999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="H24" s="0">
-        <v>12.710000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="I24" s="0">
-        <v>82.659999999999997</v>
+        <v>84.989999999999995</v>
       </c>
       <c r="J24" s="0">
-        <v>5724</v>
+        <v>1184</v>
       </c>
       <c r="K24" s="0">
-        <v>6276.3599999999997</v>
+        <v>3595.27</v>
       </c>
       <c r="L24" s="0">
-        <v>24.82</v>
+        <v>21.98</v>
       </c>
       <c r="M24" s="0">
-        <v>0.048000000000000001</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1182,40 +1212,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>65346030208</v>
+        <v>37464151182</v>
       </c>
       <c r="C25" s="0">
-        <v>80073867608</v>
+        <v>43860829543</v>
       </c>
       <c r="D25" s="0">
-        <v>1579678</v>
+        <v>770976</v>
       </c>
       <c r="E25" s="0">
-        <v>274</v>
+        <v>176</v>
       </c>
       <c r="F25" s="0">
-        <v>63590</v>
+        <v>192425</v>
       </c>
       <c r="G25" s="0">
-        <v>1.25</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="H25" s="0">
-        <v>11.67</v>
+        <v>10.890000000000001</v>
       </c>
       <c r="I25" s="0">
-        <v>81.609999999999999</v>
+        <v>85.420000000000002</v>
       </c>
       <c r="J25" s="0">
-        <v>4639</v>
+        <v>1293</v>
       </c>
       <c r="K25" s="0">
-        <v>8206.9500000000007</v>
+        <v>3405.48</v>
       </c>
       <c r="L25" s="0">
-        <v>30.23</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="M25" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.048000000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1223,40 +1253,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>11860021217</v>
+        <v>28753046860</v>
       </c>
       <c r="C26" s="0">
-        <v>15053123666</v>
+        <v>32906707555</v>
       </c>
       <c r="D26" s="0">
-        <v>2105332</v>
+        <v>856499</v>
       </c>
       <c r="E26" s="0">
-        <v>310</v>
+        <v>180</v>
       </c>
       <c r="F26" s="0">
-        <v>9996</v>
+        <v>139843</v>
       </c>
       <c r="G26" s="0">
-        <v>1.3999999999999999</v>
+        <v>3.6400000000000001</v>
       </c>
       <c r="H26" s="0">
-        <v>13.619999999999999</v>
+        <v>11.69</v>
       </c>
       <c r="I26" s="0">
-        <v>78.790000000000006</v>
+        <v>87.379999999999995</v>
       </c>
       <c r="J26" s="0">
-        <v>4859</v>
+        <v>1304</v>
       </c>
       <c r="K26" s="0">
-        <v>10408.68</v>
+        <v>3264.3800000000001</v>
       </c>
       <c r="L26" s="0">
-        <v>33.579999999999998</v>
+        <v>18.09</v>
       </c>
       <c r="M26" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.044999999999999998</v>
       </c>
     </row>
     <row r="27">
@@ -1264,40 +1294,450 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>822664314584</v>
+        <v>53043151453</v>
       </c>
       <c r="C27" s="0">
-        <v>983901365353</v>
+        <v>62042325709</v>
       </c>
       <c r="D27" s="0">
-        <v>0</v>
+        <v>775045</v>
       </c>
       <c r="E27" s="0">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="F27" s="0">
-        <v>6291915</v>
+        <v>208589</v>
       </c>
       <c r="G27" s="0">
-        <v>0</v>
+        <v>2.6099999999999999</v>
       </c>
       <c r="H27" s="0">
-        <v>0</v>
+        <v>10.359999999999999</v>
       </c>
       <c r="I27" s="0">
-        <v>83.609999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="J27" s="0">
-        <v>978</v>
+        <v>1677</v>
       </c>
       <c r="K27" s="0">
-        <v>3469.8299999999999</v>
+        <v>4269.3100000000004</v>
       </c>
       <c r="L27" s="0">
-        <v>22.91</v>
+        <v>24.030000000000001</v>
       </c>
       <c r="M27" s="0">
+        <v>0.057000000000000002</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>10755194299</v>
+      </c>
+      <c r="C28" s="0">
+        <v>12373005070</v>
+      </c>
+      <c r="D28" s="0">
+        <v>919926</v>
+      </c>
+      <c r="E28" s="0">
+        <v>224</v>
+      </c>
+      <c r="F28" s="0">
+        <v>36434</v>
+      </c>
+      <c r="G28" s="0">
+        <v>2.71</v>
+      </c>
+      <c r="H28" s="0">
+        <v>9.9000000000000004</v>
+      </c>
+      <c r="I28" s="0">
+        <v>86.920000000000002</v>
+      </c>
+      <c r="J28" s="0">
+        <v>1525</v>
+      </c>
+      <c r="K28" s="0">
+        <v>4561.8199999999997</v>
+      </c>
+      <c r="L28" s="0">
+        <v>20.469999999999999</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.049000000000000002</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>46701276480</v>
+      </c>
+      <c r="C29" s="0">
+        <v>58279479500</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1061750</v>
+      </c>
+      <c r="E29" s="0">
+        <v>219</v>
+      </c>
+      <c r="F29" s="0">
+        <v>85247</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.55</v>
+      </c>
+      <c r="H29" s="0">
+        <v>10.640000000000001</v>
+      </c>
+      <c r="I29" s="0">
+        <v>80.129999999999995</v>
+      </c>
+      <c r="J29" s="0">
+        <v>3179</v>
+      </c>
+      <c r="K29" s="0">
+        <v>5760.71</v>
+      </c>
+      <c r="L29" s="0">
+        <v>26.739999999999998</v>
+      </c>
+      <c r="M29" s="0">
         <v>0.058000000000000003</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>15240285240</v>
+      </c>
+      <c r="C30" s="0">
+        <v>19478562981</v>
+      </c>
+      <c r="D30" s="0">
+        <v>0</v>
+      </c>
+      <c r="E30" s="0">
+        <v>244</v>
+      </c>
+      <c r="F30" s="0">
+        <v>20232</v>
+      </c>
+      <c r="G30" s="0">
+        <v>0</v>
+      </c>
+      <c r="H30" s="0">
+        <v>0</v>
+      </c>
+      <c r="I30" s="0">
+        <v>78.239999999999995</v>
+      </c>
+      <c r="J30" s="0">
+        <v>3948</v>
+      </c>
+      <c r="K30" s="0">
+        <v>5665.25</v>
+      </c>
+      <c r="L30" s="0">
+        <v>23.23</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.048000000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>22134062791</v>
+      </c>
+      <c r="C31" s="0">
+        <v>27108775822</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1544660</v>
+      </c>
+      <c r="E31" s="0">
+        <v>271</v>
+      </c>
+      <c r="F31" s="0">
+        <v>29732</v>
+      </c>
+      <c r="G31" s="0">
+        <v>1.6899999999999999</v>
+      </c>
+      <c r="H31" s="0">
+        <v>12.25</v>
+      </c>
+      <c r="I31" s="0">
+        <v>81.650000000000006</v>
+      </c>
+      <c r="J31" s="0">
+        <v>3402</v>
+      </c>
+      <c r="K31" s="0">
+        <v>6329.8999999999996</v>
+      </c>
+      <c r="L31" s="0">
+        <v>23.579999999999998</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>20726284331</v>
+      </c>
+      <c r="C32" s="0">
+        <v>24947877361</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1872964</v>
+      </c>
+      <c r="E32" s="0">
+        <v>291</v>
+      </c>
+      <c r="F32" s="0">
+        <v>21923</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.6499999999999999</v>
+      </c>
+      <c r="H32" s="0">
+        <v>13.470000000000001</v>
+      </c>
+      <c r="I32" s="0">
+        <v>83.079999999999998</v>
+      </c>
+      <c r="J32" s="0">
+        <v>3907</v>
+      </c>
+      <c r="K32" s="0">
+        <v>6203.6300000000001</v>
+      </c>
+      <c r="L32" s="0">
+        <v>21.300000000000001</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.044999999999999998</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>11677501261</v>
+      </c>
+      <c r="C33" s="0">
+        <v>14262624251</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1379364</v>
+      </c>
+      <c r="E33" s="0">
+        <v>222</v>
+      </c>
+      <c r="F33" s="0">
+        <v>12956</v>
+      </c>
+      <c r="G33" s="0">
+        <v>1.25</v>
+      </c>
+      <c r="H33" s="0">
+        <v>12.289999999999999</v>
+      </c>
+      <c r="I33" s="0">
+        <v>81.870000000000005</v>
+      </c>
+      <c r="J33" s="0">
+        <v>4945</v>
+      </c>
+      <c r="K33" s="0">
+        <v>6566.8400000000001</v>
+      </c>
+      <c r="L33" s="0">
+        <v>29.5</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.058000000000000003</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>8870604925</v>
+      </c>
+      <c r="C34" s="0">
+        <v>10731443053</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1661214</v>
+      </c>
+      <c r="E34" s="0">
+        <v>253</v>
+      </c>
+      <c r="F34" s="0">
+        <v>7415</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H34" s="0">
+        <v>12.710000000000001</v>
+      </c>
+      <c r="I34" s="0">
+        <v>82.659999999999997</v>
+      </c>
+      <c r="J34" s="0">
+        <v>5724</v>
+      </c>
+      <c r="K34" s="0">
+        <v>6276.3599999999997</v>
+      </c>
+      <c r="L34" s="0">
+        <v>24.82</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.048000000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>65346030208</v>
+      </c>
+      <c r="C35" s="0">
+        <v>80073867608</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1579678</v>
+      </c>
+      <c r="E35" s="0">
+        <v>274</v>
+      </c>
+      <c r="F35" s="0">
+        <v>63590</v>
+      </c>
+      <c r="G35" s="0">
+        <v>1.25</v>
+      </c>
+      <c r="H35" s="0">
+        <v>11.67</v>
+      </c>
+      <c r="I35" s="0">
+        <v>81.609999999999999</v>
+      </c>
+      <c r="J35" s="0">
+        <v>4639</v>
+      </c>
+      <c r="K35" s="0">
+        <v>8206.9500000000007</v>
+      </c>
+      <c r="L35" s="0">
+        <v>30.23</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.060999999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
+        <v>11860021217</v>
+      </c>
+      <c r="C36" s="0">
+        <v>15053123666</v>
+      </c>
+      <c r="D36" s="0">
+        <v>2105332</v>
+      </c>
+      <c r="E36" s="0">
+        <v>310</v>
+      </c>
+      <c r="F36" s="0">
+        <v>9996</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H36" s="0">
+        <v>13.619999999999999</v>
+      </c>
+      <c r="I36" s="0">
+        <v>78.790000000000006</v>
+      </c>
+      <c r="J36" s="0">
+        <v>4859</v>
+      </c>
+      <c r="K36" s="0">
+        <v>10408.68</v>
+      </c>
+      <c r="L36" s="0">
+        <v>33.579999999999998</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
+        <v>879786246149</v>
+      </c>
+      <c r="C37" s="0">
+        <v>1053014294562</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0">
+        <v>130</v>
+      </c>
+      <c r="F37" s="0">
+        <v>7263991</v>
+      </c>
+      <c r="G37" s="0">
+        <v>0</v>
+      </c>
+      <c r="H37" s="0">
+        <v>0</v>
+      </c>
+      <c r="I37" s="0">
+        <v>83.549999999999997</v>
+      </c>
+      <c r="J37" s="0">
+        <v>918</v>
+      </c>
+      <c r="K37" s="0">
+        <v>3441.0700000000002</v>
+      </c>
+      <c r="L37" s="0">
+        <v>23.030000000000001</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.058999999999999997</v>
       </c>
     </row>
   </sheetData>
